--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487751_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487751_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8274</v>
+        <v>6.3986</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3506</v>
+        <v>6.0308</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4768</v>
+        <v>0.3677</v>
       </c>
       <c r="G2" t="n">
         <v>5.2422</v>
@@ -610,13 +610,13 @@
         <v>2.5224</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6449</v>
+        <v>1.2161</v>
       </c>
       <c r="T2" t="n">
-        <v>2.307</v>
+        <v>0.9872</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3378</v>
+        <v>0.2288</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2239</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2486</v>
+        <v>6.2429</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3274</v>
+        <v>4.0491</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9212</v>
+        <v>2.1938</v>
       </c>
       <c r="G3" t="n">
         <v>8.3756</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5646</v>
+        <v>-0.5703</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1508</v>
+        <v>-0.429</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4138</v>
+        <v>-0.1413</v>
       </c>
       <c r="V3" t="n">
         <v>0.96</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8276</v>
+        <v>4.0672</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7493</v>
+        <v>3.0706</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0783</v>
+        <v>0.9966</v>
       </c>
       <c r="G4" t="n">
         <v>3.4022</v>
@@ -766,13 +766,13 @@
         <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1346</v>
+        <v>-0.895</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0902</v>
+        <v>-0.7689</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0444</v>
+        <v>-0.1261</v>
       </c>
       <c r="V4" t="n">
         <v>0.3958</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9394</v>
+        <v>1.6187</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4548</v>
+        <v>1.2977</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4845</v>
+        <v>0.321</v>
       </c>
       <c r="G5" t="n">
         <v>1.0276</v>
@@ -844,13 +844,13 @@
         <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5819</v>
+        <v>1.2612</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.12</v>
+        <v>0.7228</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7019</v>
+        <v>0.5384</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2821</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ RODRIGUEZ</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3161</v>
+        <v>0.2735</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6323</v>
+        <v>-1.7152</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9483</v>
+        <v>1.9887</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5299</v>
+        <v>-2.0833</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9359</v>
+        <v>-2.9931</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.406</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9475</v>
+        <v>-1.7735</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9475</v>
+        <v>-1.2152</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.5583</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4175</v>
+        <v>-0.3098</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0115</v>
+        <v>-1.7779</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.406</v>
+        <v>1.4681</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3699</v>
+        <v>0.2908</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1211</v>
+        <v>-0.0014</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2488</v>
+        <v>0.2922</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2821</v>
+        <v>1.2898</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2821</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>P. HERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4599</v>
+        <v>-0.2282</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2578</v>
+        <v>0.6929</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7979</v>
+        <v>-0.9211</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0833</v>
+        <v>0.5299</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9931</v>
+        <v>0.9359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9098000000000001</v>
+        <v>-0.406</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.7735</v>
+        <v>0.9475</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2152</v>
+        <v>0.9475</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5583</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3098</v>
+        <v>-0.4175</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7779</v>
+        <v>-0.0115</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4681</v>
+        <v>-0.406</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7761</v>
+        <v>-0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9403</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4426</v>
+        <v>-0.2821</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.544</v>
+        <v>-0.0606</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1014</v>
+        <v>-0.2215</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2898</v>
+        <v>-0.2821</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.066</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.742</v>
+        <v>-0.5085</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7964</v>
+        <v>-1.5356</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0544</v>
+        <v>1.0271</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7891</v>
@@ -1078,13 +1078,13 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0305</v>
+        <v>0.203</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1817</v>
+        <v>0.0791</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1512</v>
+        <v>0.1239</v>
       </c>
       <c r="V8" t="n">
         <v>0.6597</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. KHIVRENKO</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8337</v>
+        <v>-0.5985</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7503</v>
+        <v>0.0103</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0834</v>
+        <v>-0.6089</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0939</v>
+        <v>-0.2919</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1617</v>
+        <v>0.2826</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0677</v>
+        <v>-0.5745</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2188</v>
+        <v>0.9897</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>1.553</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8119</v>
+        <v>-0.5633</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3127</v>
+        <v>-1.2816</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5685</v>
+        <v>-1.2704</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2558</v>
+        <v>-0.0111</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7761</v>
+        <v>2.3284</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6122</v>
+        <v>0.4127</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0011</v>
+        <v>0.2804</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6111</v>
+        <v>0.1324</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1579</v>
+        <v>-1.8836</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.0955</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1579</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>M. KHIVRENKO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3986</v>
+        <v>-1.2521</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5718</v>
+        <v>-0.8689</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8269</v>
+        <v>-0.3832</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2919</v>
+        <v>-0.0939</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2826</v>
+        <v>-1.1617</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5745</v>
+        <v>1.0677</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9897</v>
+        <v>0.2188</v>
       </c>
       <c r="K10" t="n">
-        <v>1.553</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5633</v>
+        <v>0.8119</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2816</v>
+        <v>-0.3127</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2704</v>
+        <v>-0.5685</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0111</v>
+        <v>0.2558</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3874</v>
+        <v>0.1938</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3017</v>
+        <v>-0.1175</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0857</v>
+        <v>0.3113</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8836</v>
+        <v>-1.1579</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0955</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.788</v>
+        <v>-1.1579</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.603</v>
+        <v>-1.5241</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8884</v>
+        <v>-0.7277</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7146</v>
+        <v>-0.7964</v>
       </c>
       <c r="G11" t="n">
         <v>-1.415</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.188</v>
+        <v>-0.1091</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3028</v>
+        <v>-0.1422</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1149</v>
+        <v>0.0331</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9573</v>
+        <v>-2.3122</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4757</v>
+        <v>-1.294</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4815</v>
+        <v>-1.0182</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8567</v>
@@ -1390,13 +1390,13 @@
         <v>0.5821</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0606</v>
+        <v>-0.4155</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3017</v>
+        <v>-0.12</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7588</v>
+        <v>-0.2955</v>
       </c>
       <c r="V12" t="n">
         <v>0.3481</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0071</v>
+        <v>-3.8348</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.2136</v>
+        <v>-6.6325</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2064</v>
+        <v>2.7976</v>
       </c>
       <c r="G13" t="n">
         <v>-5.3227</v>
@@ -1468,13 +1468,13 @@
         <v>2.3284</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7037</v>
+        <v>0.876</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7907</v>
+        <v>0.3718</v>
       </c>
       <c r="U13" t="n">
-        <v>0.913</v>
+        <v>0.5042</v>
       </c>
       <c r="V13" t="n">
         <v>0.6119</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.5253</v>
+        <v>8.342500000000003</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5604000000000013</v>
+        <v>2.3775</v>
       </c>
       <c r="F14" t="n">
-        <v>5.964799999999999</v>
+        <v>5.9647</v>
       </c>
       <c r="G14" t="n">
         <v>6.724900000000003</v>
@@ -1537,7 +1537,7 @@
         <v>5.227399999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>-2.775557561562891e-16</v>
       </c>
       <c r="Q14" t="n">
         <v>-15.5227</v>
@@ -1546,19 +1546,19 @@
         <v>15.5226</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3644999999999996</v>
+        <v>2.1816</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0152</v>
+        <v>0.8017</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3798</v>
+        <v>1.3799</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5642999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>5.928399999999999</v>
+        <v>5.9284</v>
       </c>
       <c r="X14" t="n">
         <v>-6.492399999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2558</v>
+        <v>3.9917</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5243</v>
+        <v>2.7235</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7315</v>
+        <v>1.2682</v>
       </c>
       <c r="G15" t="n">
         <v>0.7948</v>
@@ -1624,13 +1624,13 @@
         <v>2.5224</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0729</v>
+        <v>-0.1912</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5484</v>
+        <v>-0.2524</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5245</v>
+        <v>0.0612</v>
       </c>
       <c r="V15" t="n">
         <v>1.8358</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. VAZQUEZ JEREZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6452</v>
+        <v>1.6539</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7216</v>
+        <v>-0.2743</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0763</v>
+        <v>1.9282</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4496</v>
+        <v>0.4233</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1971</v>
+        <v>0.8815</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.4582</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9802</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>1.899</v>
+        <v>0.9392</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0356</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5306</v>
+        <v>-0.4804</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7019</v>
+        <v>-0.0577</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8286</v>
+        <v>-0.4227</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5821</v>
+        <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1956</v>
+        <v>0.0665</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7115</v>
+        <v>-0.2078</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4841</v>
+        <v>0.2743</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. FERNÁNDEZ GÓMEZ</t>
+          <t>I. MENCARA JIMENEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.502</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9034</v>
+        <v>1.6461</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4054</v>
+        <v>-0.8089</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6254</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.463</v>
+        <v>1.8611</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1624</v>
+        <v>-1.0783</v>
       </c>
       <c r="J17" t="n">
-        <v>1.14</v>
+        <v>3.0094</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5438</v>
+        <v>2.9865</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5962</v>
+        <v>0.0228</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-2.2266</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0808</v>
+        <v>-1.1254</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4338</v>
+        <v>-1.1011</v>
       </c>
       <c r="P17" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-3.8806</v>
-      </c>
       <c r="R17" t="n">
-        <v>2.9105</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6124</v>
+        <v>-0.3337</v>
       </c>
       <c r="T17" t="n">
-        <v>0.379</v>
+        <v>-0.3931</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2333</v>
+        <v>0.0595</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2343</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4582</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.8264</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7832</v>
+        <v>1.4829</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.82</v>
+        <v>-0.6565</v>
       </c>
       <c r="G18" t="n">
         <v>1.4865</v>
@@ -1858,13 +1858,13 @@
         <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5946</v>
+        <v>0.4579</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4856</v>
+        <v>0.1853</v>
       </c>
       <c r="U18" t="n">
-        <v>0.109</v>
+        <v>0.2725</v>
       </c>
       <c r="V18" t="n">
         <v>-1.506</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>A. FERNÁNDEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.502</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.975</v>
+        <v>-1.3038</v>
       </c>
       <c r="F19" t="n">
-        <v>1.792</v>
+        <v>1.8058</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4233</v>
+        <v>0.6254</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8815</v>
+        <v>0.463</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4582</v>
+        <v>0.1624</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9036999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9392</v>
+        <v>0.5438</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0356</v>
+        <v>0.5962</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4804</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0577</v>
+        <v>-0.0808</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4227</v>
+        <v>-0.4338</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1344</v>
+        <v>2.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7705</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9085</v>
+        <v>-0.0214</v>
       </c>
       <c r="U19" t="n">
-        <v>0.138</v>
+        <v>0.6337</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2343</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.4582</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. MENCARA JIMENEZ</t>
+          <t>D. VAZQUEZ JEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.528</v>
+        <v>0.4896</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4459</v>
+        <v>1.6205</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9179</v>
+        <v>-1.1309</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.4496</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8611</v>
+        <v>1.1971</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0783</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>3.0094</v>
+        <v>1.9802</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9865</v>
+        <v>1.899</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0228</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2266</v>
+        <v>-1.5306</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1254</v>
+        <v>-0.7019</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1011</v>
+        <v>-0.8286</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3881</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6429</v>
+        <v>1.04</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5933</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0496</v>
+        <v>0.4296</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4182</v>
+        <v>-1.327</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1624</v>
+        <v>-0.9622000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2557</v>
+        <v>-0.3647</v>
       </c>
       <c r="G21" t="n">
         <v>-3.3208</v>
@@ -2092,13 +2092,13 @@
         <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2914</v>
+        <v>-0.2002</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4722</v>
+        <v>-0.272</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1808</v>
+        <v>0.0718</v>
       </c>
       <c r="V21" t="n">
         <v>1.2239</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.007</v>
+        <v>-2.4431</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1999</v>
+        <v>-1.7995</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8072</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-2.712</v>
@@ -2170,13 +2170,13 @@
         <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2369</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8356</v>
+        <v>-0.4352</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4013</v>
+        <v>-0.2378</v>
       </c>
       <c r="V22" t="n">
         <v>0.9418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0241</v>
+        <v>-4.5786</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2787</v>
+        <v>-4.0785</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7454</v>
+        <v>-0.5001</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4253</v>
@@ -2248,13 +2248,13 @@
         <v>1.5523</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1824</v>
+        <v>-0.7369</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4229</v>
+        <v>-0.2227</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7595</v>
+        <v>-0.5142</v>
       </c>
       <c r="V23" t="n">
         <v>0.9418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.7872</v>
+        <v>-6.4775</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.9203</v>
+        <v>-5.0194</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8669</v>
+        <v>-1.4581</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8294</v>
@@ -2326,13 +2326,13 @@
         <v>2.1344</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.716</v>
+        <v>-0.4063</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2719</v>
+        <v>-0.371</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4441</v>
+        <v>-0.0353</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4955</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.525300000000001</v>
+        <v>-6.525399999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.964700000000001</v>
+        <v>-5.9647</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5604999999999996</v>
+        <v>-0.5606</v>
       </c>
       <c r="G25" t="n">
         <v>-6.725099999999999</v>
@@ -2383,7 +2383,7 @@
         <v>9.672200000000002</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.227300000000001</v>
+        <v>-5.2273</v>
       </c>
       <c r="M25" t="n">
         <v>-11.1702</v>
@@ -2395,7 +2395,7 @@
         <v>-8.286300000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>0.0001000000000004331</v>
       </c>
       <c r="Q25" t="n">
         <v>-15.5227</v>
@@ -2404,13 +2404,13 @@
         <v>15.5228</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3645999999999996</v>
+        <v>-0.3643999999999999</v>
       </c>
       <c r="T25" t="n">
         <v>-1.3799</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0152</v>
+        <v>1.0153</v>
       </c>
       <c r="V25" t="n">
         <v>0.5642000000000005</v>
